--- a/reports/pdf_rolling5_20260908.xlsx
+++ b/reports/pdf_rolling5_20260908.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,584억   ·   현금 41억(0.9%)      오늘 2026-09-08  vs  5일전 2026-09-01      매수 14종목  /  매도 8종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,584억   ·   현금 21억(0.4%)      오늘 2026-09-08  vs  5일전 2026-09-01      매수 14종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1071,23 +1071,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>834724800</v>
+        <v>1238702400</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>0.93%→1.07%</t>
+          <t>0.99%→1.15%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>58→70</t>
+          <t>39→51</t>
         </is>
       </c>
       <c r="G16" s="17" t="n"/>
@@ -1099,23 +1099,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1238702400</v>
+        <v>834724800</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>0.99%→1.15%</t>
+          <t>0.93%→1.07%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>39→51</t>
+          <t>58→70</t>
         </is>
       </c>
       <c r="G17" s="17" t="n"/>
@@ -1183,7 +1183,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,588억   ·   현금 88억(2.4%)      오늘 2026-09-08  vs  5일전 2026-09-01      매수 4종목  /  매도 5종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,588억   ·   현금 44억(1.2%)      오늘 2026-09-08  vs  5일전 2026-09-01      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1476,7 +1476,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,559억   ·   현금 69억(2.7%)      오늘 2026-09-08  vs  5일전 2026-09-01      매수 12종목  /  매도 10종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,559억   ·   현금 34억(1.3%)      오늘 2026-09-08  vs  5일전 2026-09-01      매수 12종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1829,23 +1829,23 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈  (신규)</t>
         </is>
       </c>
       <c r="B39" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>2710447500</v>
+        <v>3125047500</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>2.26%→3.58%</t>
+          <t>0.00%→1.24%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>35→50</t>
+          <t>0→15</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
@@ -1873,23 +1873,23 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>로보티즈  (신규)</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3125047500</v>
+        <v>2710447500</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.24%</t>
+          <t>2.26%→3.58%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>0→15</t>
+          <t>35→50</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -1938,23 +1938,23 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-29</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-1374675400</v>
+        <v>-2039970200</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>1.55%→0.96%</t>
+          <t>1.81%→0.84%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>80→51</t>
+          <t>59→30</t>
         </is>
       </c>
     </row>
@@ -1982,23 +1982,23 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-29</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-2039970200</v>
+        <v>-1374675400</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>1.81%→0.84%</t>
+          <t>1.55%→0.96%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>59→30</t>
+          <t>80→51</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,028억   ·   현금 32억(1.6%)      오늘 2026-09-08  vs  5일전 2026-09-01      매수 6종목  /  매도 11종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,028억   ·   현금 16억(0.8%)      오늘 2026-09-08  vs  5일전 2026-09-01      매수 6종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
@@ -2554,7 +2554,7 @@
     <row r="61" ht="19" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 274억   ·   현금 3억(1.0%)      오늘 2026-09-08  vs  5일전 2026-09-01      매수 9종목  /  매도 10종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 274억   ·   현금 1억(0.5%)      오늘 2026-09-08  vs  5일전 2026-09-01      매수 9종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B61" s="4" t="n"/>
@@ -2775,23 +2775,23 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>69310500</v>
+        <v>78498000</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>0.96%→1.21%</t>
+          <t>2.64%→2.92%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>79→100</t>
+          <t>192→213</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
@@ -2819,23 +2819,23 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>78498000</v>
+        <v>69310500</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>2.64%→2.92%</t>
+          <t>0.96%→1.21%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>192→213</t>
+          <t>79→100</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -3067,7 +3067,7 @@
     <row r="75" ht="19" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 502억   ·   현금 8억(1.6%)      오늘 2026-09-08  vs  5일전 2026-09-01      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 502억   ·   현금 4억(0.8%)      오늘 2026-09-08  vs  5일전 2026-09-01      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B75" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260908.xlsx
+++ b/reports/pdf_rolling5_20260908.xlsx
@@ -1829,23 +1829,23 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>로보티즈  (신규)</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B39" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>3125047500</v>
+        <v>2710447500</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.24%</t>
+          <t>2.26%→3.58%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>0→15</t>
+          <t>35→50</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
@@ -1873,23 +1873,23 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈  (신규)</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>2710447500</v>
+        <v>3125047500</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>2.26%→3.58%</t>
+          <t>0.00%→1.24%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>35→50</t>
+          <t>0→15</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -2775,23 +2775,23 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>78498000</v>
+        <v>69310500</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>2.64%→2.92%</t>
+          <t>0.96%→1.21%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>192→213</t>
+          <t>79→100</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
@@ -2819,23 +2819,23 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>69310500</v>
+        <v>78498000</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>0.96%→1.21%</t>
+          <t>2.64%→2.92%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>79→100</t>
+          <t>192→213</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260908.xlsx
+++ b/reports/pdf_rolling5_20260908.xlsx
@@ -59,13 +59,13 @@
       <color rgb="000070C0"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="8">
@@ -171,11 +171,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-09-01 ~ 2026-09-08  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-09-01 ~ 2026-09-08  (최근 5거래일)  ·  캡처 5/7  ·  대기: PLUS, TIGER</t>
         </is>
       </c>
     </row>
@@ -1829,23 +1829,23 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈  (신규)</t>
         </is>
       </c>
       <c r="B39" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>2710447500</v>
+        <v>3125047500</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>2.26%→3.58%</t>
+          <t>0.00%→1.24%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>35→50</t>
+          <t>0→15</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
@@ -1873,23 +1873,23 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>로보티즈  (신규)</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3125047500</v>
+        <v>2710447500</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.24%</t>
+          <t>2.26%→3.58%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>0→15</t>
+          <t>35→50</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -2552,581 +2552,83 @@
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 274억   ·   현금 1억(0.5%)      오늘 2026-09-08  vs  5일전 2026-09-01      매수 9종목  /  매도 10종목</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="n"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-      <c r="F61" s="4" t="n"/>
-      <c r="G61" s="4" t="n"/>
-      <c r="H61" s="4" t="n"/>
-      <c r="I61" s="4" t="n"/>
-      <c r="J61" s="4" t="n"/>
-      <c r="K61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="n"/>
-      <c r="C62" s="6" t="n"/>
-      <c r="D62" s="6" t="n"/>
-      <c r="E62" s="6" t="n"/>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="8" t="n"/>
-      <c r="J62" s="8" t="n"/>
-      <c r="K62" s="8" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B63" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C63" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H63" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J63" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K63" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="n"/>
+      <c r="C61" s="19" t="n"/>
+      <c r="D61" s="19" t="n"/>
+      <c r="E61" s="19" t="n"/>
+      <c r="F61" s="19" t="n"/>
+      <c r="G61" s="19" t="n"/>
+      <c r="H61" s="19" t="n"/>
+      <c r="I61" s="19" t="n"/>
+      <c r="J61" s="19" t="n"/>
+      <c r="K61" s="19" t="n"/>
+    </row>
+    <row r="63" ht="19" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 502억   ·   현금 4억(0.8%)      오늘 2026-09-08  vs  5일전 2026-09-01      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="n"/>
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="4" t="n"/>
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="n"/>
+      <c r="G63" s="4" t="n"/>
+      <c r="H63" s="4" t="n"/>
+      <c r="I63" s="4" t="n"/>
+      <c r="J63" s="4" t="n"/>
+      <c r="K63" s="4" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="B64" s="11" t="n">
-        <v>58</v>
-      </c>
-      <c r="C64" s="11" t="n">
-        <v>148596000</v>
-      </c>
-      <c r="D64" s="12" t="inlineStr">
-        <is>
-          <t>7.01%→7.54%</t>
-        </is>
-      </c>
-      <c r="E64" s="13" t="inlineStr">
-        <is>
-          <t>744→802</t>
-        </is>
-      </c>
-      <c r="G64" s="14" t="inlineStr">
-        <is>
-          <t>더블유씨피</t>
-        </is>
-      </c>
-      <c r="H64" s="15" t="n">
-        <v>-141</v>
-      </c>
-      <c r="I64" s="15" t="n">
-        <v>-99489600</v>
-      </c>
-      <c r="J64" s="16" t="inlineStr">
-        <is>
-          <t>7.74%→7.36%</t>
-        </is>
-      </c>
-      <c r="K64" s="13" t="inlineStr">
-        <is>
-          <t>2,984→2,843</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>에프앤가이드</t>
-        </is>
-      </c>
-      <c r="B65" s="11" t="n">
-        <v>47</v>
-      </c>
-      <c r="C65" s="11" t="n">
-        <v>55107500</v>
-      </c>
-      <c r="D65" s="12" t="inlineStr">
-        <is>
-          <t>3.35%→3.55%</t>
-        </is>
-      </c>
-      <c r="E65" s="13" t="inlineStr">
-        <is>
-          <t>777→824</t>
-        </is>
-      </c>
-      <c r="G65" s="14" t="inlineStr">
-        <is>
-          <t>한선엔지니어링</t>
-        </is>
-      </c>
-      <c r="H65" s="15" t="n">
-        <v>-93</v>
-      </c>
-      <c r="I65" s="15" t="n">
-        <v>-66336900</v>
-      </c>
-      <c r="J65" s="16" t="inlineStr">
-        <is>
-          <t>1.04%→0.80%</t>
-        </is>
-      </c>
-      <c r="K65" s="13" t="inlineStr">
-        <is>
-          <t>397→304</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>하나머티리얼즈</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="n">
-        <v>41</v>
-      </c>
-      <c r="C66" s="11" t="n">
-        <v>150388000</v>
-      </c>
-      <c r="D66" s="12" t="inlineStr">
-        <is>
-          <t>0.78%→1.33%</t>
-        </is>
-      </c>
-      <c r="E66" s="13" t="inlineStr">
-        <is>
-          <t>58→99</t>
-        </is>
-      </c>
-      <c r="G66" s="14" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="H66" s="15" t="n">
-        <v>-65</v>
-      </c>
-      <c r="I66" s="15" t="n">
-        <v>-102147500</v>
-      </c>
-      <c r="J66" s="16" t="inlineStr">
-        <is>
-          <t>5.63%→5.24%</t>
-        </is>
-      </c>
-      <c r="K66" s="13" t="inlineStr">
-        <is>
-          <t>974→909</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>실리콘투</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="C67" s="11" t="n">
-        <v>69310500</v>
-      </c>
-      <c r="D67" s="12" t="inlineStr">
-        <is>
-          <t>0.96%→1.21%</t>
-        </is>
-      </c>
-      <c r="E67" s="13" t="inlineStr">
-        <is>
-          <t>79→100</t>
-        </is>
-      </c>
-      <c r="G67" s="14" t="inlineStr">
-        <is>
-          <t>한중엔시에스</t>
-        </is>
-      </c>
-      <c r="H67" s="15" t="n">
-        <v>-27</v>
-      </c>
-      <c r="I67" s="15" t="n">
-        <v>-76545000</v>
-      </c>
-      <c r="J67" s="16" t="inlineStr">
-        <is>
-          <t>2.76%→2.48%</t>
-        </is>
-      </c>
-      <c r="K67" s="13" t="inlineStr">
-        <is>
-          <t>265→238</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t>브이엠</t>
-        </is>
-      </c>
-      <c r="B68" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="C68" s="11" t="n">
-        <v>78498000</v>
-      </c>
-      <c r="D68" s="12" t="inlineStr">
-        <is>
-          <t>2.64%→2.92%</t>
-        </is>
-      </c>
-      <c r="E68" s="13" t="inlineStr">
-        <is>
-          <t>192→213</t>
-        </is>
-      </c>
-      <c r="G68" s="14" t="inlineStr">
-        <is>
-          <t>비나텍</t>
-        </is>
-      </c>
-      <c r="H68" s="15" t="n">
-        <v>-17</v>
-      </c>
-      <c r="I68" s="15" t="n">
-        <v>-76398000</v>
-      </c>
-      <c r="J68" s="16" t="inlineStr">
-        <is>
-          <t>1.87%→1.58%</t>
-        </is>
-      </c>
-      <c r="K68" s="13" t="inlineStr">
-        <is>
-          <t>113→96</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>엘티씨</t>
-        </is>
-      </c>
-      <c r="B69" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="C69" s="11" t="n">
-        <v>39270000</v>
-      </c>
-      <c r="D69" s="12" t="inlineStr">
-        <is>
-          <t>1.16%→1.30%</t>
-        </is>
-      </c>
-      <c r="E69" s="13" t="inlineStr">
-        <is>
-          <t>120→135</t>
-        </is>
-      </c>
-      <c r="G69" s="14" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="H69" s="15" t="n">
-        <v>-16</v>
-      </c>
-      <c r="I69" s="15" t="n">
-        <v>-45472000</v>
-      </c>
-      <c r="J69" s="16" t="inlineStr">
-        <is>
-          <t>3.91%→3.73%</t>
-        </is>
-      </c>
-      <c r="K69" s="13" t="inlineStr">
-        <is>
-          <t>374→358</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="10" t="inlineStr">
-        <is>
-          <t>씨엠티엑스</t>
-        </is>
-      </c>
-      <c r="B70" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="C70" s="11" t="n">
-        <v>73598000</v>
-      </c>
-      <c r="D70" s="12" t="inlineStr">
-        <is>
-          <t>0.95%→1.22%</t>
-        </is>
-      </c>
-      <c r="E70" s="13" t="inlineStr">
-        <is>
-          <t>49→63</t>
-        </is>
-      </c>
-      <c r="G70" s="14" t="inlineStr">
-        <is>
-          <t>HPSP</t>
-        </is>
-      </c>
-      <c r="H70" s="15" t="n">
-        <v>-10</v>
-      </c>
-      <c r="I70" s="15" t="n">
-        <v>-37310000</v>
-      </c>
-      <c r="J70" s="16" t="inlineStr">
-        <is>
-          <t>1.44%→1.30%</t>
-        </is>
-      </c>
-      <c r="K70" s="13" t="inlineStr">
-        <is>
-          <t>105→95</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t>원익머트리얼즈</t>
-        </is>
-      </c>
-      <c r="B71" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="C71" s="11" t="n">
-        <v>24717000</v>
-      </c>
-      <c r="D71" s="12" t="inlineStr">
-        <is>
-          <t>2.07%→2.16%</t>
-        </is>
-      </c>
-      <c r="E71" s="13" t="inlineStr">
-        <is>
-          <t>251→262</t>
-        </is>
-      </c>
-      <c r="G71" s="14" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="H71" s="15" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I71" s="15" t="n">
-        <v>-65520000</v>
-      </c>
-      <c r="J71" s="16" t="inlineStr">
-        <is>
-          <t>3.89%→3.65%</t>
-        </is>
-      </c>
-      <c r="K71" s="13" t="inlineStr">
-        <is>
-          <t>97→91</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="10" t="inlineStr">
-        <is>
-          <t>이오테크닉스</t>
-        </is>
-      </c>
-      <c r="B72" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C72" s="11" t="n">
-        <v>95760000</v>
-      </c>
-      <c r="D72" s="12" t="inlineStr">
-        <is>
-          <t>0.82%→1.17%</t>
-        </is>
-      </c>
-      <c r="E72" s="13" t="inlineStr">
-        <is>
-          <t>7→10</t>
-        </is>
-      </c>
-      <c r="G72" s="14" t="inlineStr">
-        <is>
-          <t>코스메카코리아</t>
-        </is>
-      </c>
-      <c r="H72" s="15" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I72" s="15" t="n">
-        <v>-45185000</v>
-      </c>
-      <c r="J72" s="16" t="inlineStr">
-        <is>
-          <t>0.37%→0.20%</t>
-        </is>
-      </c>
-      <c r="K72" s="13" t="inlineStr">
-        <is>
-          <t>11→6</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="17" t="n"/>
-      <c r="B73" s="17" t="n"/>
-      <c r="C73" s="17" t="n"/>
-      <c r="D73" s="17" t="n"/>
-      <c r="E73" s="17" t="n"/>
-      <c r="G73" s="14" t="inlineStr">
-        <is>
-          <t>파마리서치  (편출)</t>
-        </is>
-      </c>
-      <c r="H73" s="15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I73" s="15" t="n">
-        <v>-79065000</v>
-      </c>
-      <c r="J73" s="16" t="inlineStr">
-        <is>
-          <t>0.29%→0.00%</t>
-        </is>
-      </c>
-      <c r="K73" s="13" t="inlineStr">
-        <is>
-          <t>3→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="19" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 502억   ·   현금 4억(0.8%)      오늘 2026-09-08  vs  5일전 2026-09-01      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="n"/>
-      <c r="C75" s="4" t="n"/>
-      <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="n"/>
-      <c r="F75" s="4" t="n"/>
-      <c r="G75" s="4" t="n"/>
-      <c r="H75" s="4" t="n"/>
-      <c r="I75" s="4" t="n"/>
-      <c r="J75" s="4" t="n"/>
-      <c r="K75" s="4" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="18" t="inlineStr">
+      <c r="A64" s="20" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="19" customHeight="1">
-      <c r="A78" s="19" t="inlineStr">
+    <row r="66" ht="19" customHeight="1">
+      <c r="A66" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B78" s="20" t="n"/>
-      <c r="C78" s="20" t="n"/>
-      <c r="D78" s="20" t="n"/>
-      <c r="E78" s="20" t="n"/>
-      <c r="F78" s="20" t="n"/>
-      <c r="G78" s="20" t="n"/>
-      <c r="H78" s="20" t="n"/>
-      <c r="I78" s="20" t="n"/>
-      <c r="J78" s="20" t="n"/>
-      <c r="K78" s="20" t="n"/>
+      <c r="B66" s="19" t="n"/>
+      <c r="C66" s="19" t="n"/>
+      <c r="D66" s="19" t="n"/>
+      <c r="E66" s="19" t="n"/>
+      <c r="F66" s="19" t="n"/>
+      <c r="G66" s="19" t="n"/>
+      <c r="H66" s="19" t="n"/>
+      <c r="I66" s="19" t="n"/>
+      <c r="J66" s="19" t="n"/>
+      <c r="K66" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="A1:K1"/>
+  <mergeCells count="18">
     <mergeCell ref="A61:K61"/>
-    <mergeCell ref="A78:K78"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="G62:K62"/>
-    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A66:K66"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="A64:K64"/>
+    <mergeCell ref="G47:K47"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A63:K63"/>
     <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A76:K76"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="G22:K22"/>
+    <mergeCell ref="G31:K31"/>
     <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A1:K1"/>
     <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A62:E62"/>
-    <mergeCell ref="G47:K47"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="G31:K31"/>
-    <mergeCell ref="G22:K22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260908.xlsx
+++ b/reports/pdf_rolling5_20260908.xlsx
@@ -59,13 +59,13 @@
       <color rgb="000070C0"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="8">
@@ -171,11 +171,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-09-01 ~ 2026-09-08  (최근 5거래일)  ·  캡처 5/7  ·  대기: PLUS, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-09-01 ~ 2026-09-08  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -2552,83 +2552,581 @@
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
-      <c r="A61" s="18" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B61" s="19" t="n"/>
-      <c r="C61" s="19" t="n"/>
-      <c r="D61" s="19" t="n"/>
-      <c r="E61" s="19" t="n"/>
-      <c r="F61" s="19" t="n"/>
-      <c r="G61" s="19" t="n"/>
-      <c r="H61" s="19" t="n"/>
-      <c r="I61" s="19" t="n"/>
-      <c r="J61" s="19" t="n"/>
-      <c r="K61" s="19" t="n"/>
-    </row>
-    <row r="63" ht="19" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 274억   ·   현금 1억(0.5%)      오늘 2026-09-08  vs  5일전 2026-09-01      매수 9종목  /  매도 10종목</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n"/>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="n"/>
+      <c r="E61" s="4" t="n"/>
+      <c r="F61" s="4" t="n"/>
+      <c r="G61" s="4" t="n"/>
+      <c r="H61" s="4" t="n"/>
+      <c r="I61" s="4" t="n"/>
+      <c r="J61" s="4" t="n"/>
+      <c r="K61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K63" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>148596000</v>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>7.01%→7.54%</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>744→802</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>더블유씨피</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>-141</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>-99489600</v>
+      </c>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>7.74%→7.36%</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>2,984→2,843</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>55107500</v>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>3.35%→3.55%</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>777→824</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>한선엔지니어링</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>-93</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>-66336900</v>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>1.04%→0.80%</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>397→304</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>하나머티리얼즈</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>150388000</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>0.78%→1.33%</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>58→99</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H66" s="15" t="n">
+        <v>-65</v>
+      </c>
+      <c r="I66" s="15" t="n">
+        <v>-102147500</v>
+      </c>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>5.63%→5.24%</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>974→909</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>69310500</v>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>0.96%→1.21%</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>79→100</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>한중엔시에스</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I67" s="15" t="n">
+        <v>-76545000</v>
+      </c>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>2.76%→2.48%</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>265→238</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>78498000</v>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>2.64%→2.92%</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>192→213</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="H68" s="15" t="n">
+        <v>-17</v>
+      </c>
+      <c r="I68" s="15" t="n">
+        <v>-76398000</v>
+      </c>
+      <c r="J68" s="16" t="inlineStr">
+        <is>
+          <t>1.87%→1.58%</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="inlineStr">
+        <is>
+          <t>113→96</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>39270000</v>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>1.16%→1.30%</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>120→135</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I69" s="15" t="n">
+        <v>-45472000</v>
+      </c>
+      <c r="J69" s="16" t="inlineStr">
+        <is>
+          <t>3.91%→3.73%</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t>374→358</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>씨엠티엑스</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>73598000</v>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>0.95%→1.22%</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>49→63</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I70" s="15" t="n">
+        <v>-37310000</v>
+      </c>
+      <c r="J70" s="16" t="inlineStr">
+        <is>
+          <t>1.44%→1.30%</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>105→95</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>원익머트리얼즈</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>24717000</v>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>2.07%→2.16%</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>251→262</t>
+        </is>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I71" s="15" t="n">
+        <v>-65520000</v>
+      </c>
+      <c r="J71" s="16" t="inlineStr">
+        <is>
+          <t>3.89%→3.65%</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>97→91</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>이오테크닉스</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>95760000</v>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>0.82%→1.17%</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>7→10</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>코스메카코리아</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I72" s="15" t="n">
+        <v>-45185000</v>
+      </c>
+      <c r="J72" s="16" t="inlineStr">
+        <is>
+          <t>0.37%→0.20%</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>11→6</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="17" t="n"/>
+      <c r="B73" s="17" t="n"/>
+      <c r="C73" s="17" t="n"/>
+      <c r="D73" s="17" t="n"/>
+      <c r="E73" s="17" t="n"/>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>파마리서치  (편출)</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I73" s="15" t="n">
+        <v>-79065000</v>
+      </c>
+      <c r="J73" s="16" t="inlineStr">
+        <is>
+          <t>0.29%→0.00%</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>3→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="19" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 502억   ·   현금 4억(0.8%)      오늘 2026-09-08  vs  5일전 2026-09-01      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B63" s="4" t="n"/>
-      <c r="C63" s="4" t="n"/>
-      <c r="D63" s="4" t="n"/>
-      <c r="E63" s="4" t="n"/>
-      <c r="F63" s="4" t="n"/>
-      <c r="G63" s="4" t="n"/>
-      <c r="H63" s="4" t="n"/>
-      <c r="I63" s="4" t="n"/>
-      <c r="J63" s="4" t="n"/>
-      <c r="K63" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="20" t="inlineStr">
+      <c r="B75" s="4" t="n"/>
+      <c r="C75" s="4" t="n"/>
+      <c r="D75" s="4" t="n"/>
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="n"/>
+      <c r="G75" s="4" t="n"/>
+      <c r="H75" s="4" t="n"/>
+      <c r="I75" s="4" t="n"/>
+      <c r="J75" s="4" t="n"/>
+      <c r="K75" s="4" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="19" customHeight="1">
-      <c r="A66" s="18" t="inlineStr">
+    <row r="78" ht="19" customHeight="1">
+      <c r="A78" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B66" s="19" t="n"/>
-      <c r="C66" s="19" t="n"/>
-      <c r="D66" s="19" t="n"/>
-      <c r="E66" s="19" t="n"/>
-      <c r="F66" s="19" t="n"/>
-      <c r="G66" s="19" t="n"/>
-      <c r="H66" s="19" t="n"/>
-      <c r="I66" s="19" t="n"/>
-      <c r="J66" s="19" t="n"/>
-      <c r="K66" s="19" t="n"/>
+      <c r="B78" s="20" t="n"/>
+      <c r="C78" s="20" t="n"/>
+      <c r="D78" s="20" t="n"/>
+      <c r="E78" s="20" t="n"/>
+      <c r="F78" s="20" t="n"/>
+      <c r="G78" s="20" t="n"/>
+      <c r="H78" s="20" t="n"/>
+      <c r="I78" s="20" t="n"/>
+      <c r="J78" s="20" t="n"/>
+      <c r="K78" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="20">
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="A1:K1"/>
     <mergeCell ref="A61:K61"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A66:K66"/>
+    <mergeCell ref="A78:K78"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="G62:K62"/>
+    <mergeCell ref="A75:K75"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="A64:K64"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A76:K76"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A62:E62"/>
     <mergeCell ref="G47:K47"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A63:K63"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="G31:K31"/>
     <mergeCell ref="G22:K22"/>
-    <mergeCell ref="G31:K31"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
